--- a/JsonConverter/ExcelFiles/Relic.xlsx
+++ b/JsonConverter/ExcelFiles/Relic.xlsx
@@ -572,9 +572,9 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">장비의 기운을 감지해 찾아내는 직관적인 탐색 도구입니다</t>
     </r>
@@ -620,44 +620,25 @@
     <t xml:space="preserve">RELIC_EXPGAINBONUS_02</t>
   </si>
   <si>
-    <t xml:space="preserve">고카페인 커피</t>
+    <t xml:space="preserve">마왕의 과외 숙제</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마왕이 직접 내준 숙제. 하기 싫어도 경험치는 얻습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELIC_EXPGAINBONUS_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">컨닝 페이퍼</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">잠을 쫓고 뇌세포를 강제로 깨워 사냥하게 만듭니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">RELIC_EXPGAINBONUS_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">컨닝 페이퍼</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="129"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">실전에서 바로 써먹을 수 있는 팁들이 적혀 있어 경험치를 빨르게 획득합니다</t>
     </r>
@@ -747,7 +728,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -771,13 +752,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -842,15 +816,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -980,15 +954,15 @@
   <dimension ref="A1:I63"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="71.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="71.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2436,7 +2410,7 @@
       <c r="A57" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -2454,7 +2428,7 @@
       <c r="G57" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I57" s="2" t="s">
+      <c r="I57" s="3" t="s">
         <v>194</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/Relic.xlsx
+++ b/JsonConverter/ExcelFiles/Relic.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="273">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
@@ -82,6 +82,9 @@
     <t xml:space="preserve">Common</t>
   </si>
   <si>
+    <t xml:space="preserve">Attack_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">용사 몰래 밥에 섞어 넣는 마왕 특제 영양제. 공격력이 증가합니다.</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t xml:space="preserve">Rare</t>
   </si>
   <si>
+    <t xml:space="preserve">Attack_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">한 숟갈만 먹어도 힘이 난다는 마왕성 특제 양념. 공격력이 증가합니다.</t>
   </si>
   <si>
@@ -106,6 +112,9 @@
     <t xml:space="preserve">Epic</t>
   </si>
   <si>
+    <t xml:space="preserve">Attack_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">정체를 알 수 없는 보충제. 일단 근육은 조금 생깁니다.</t>
   </si>
   <si>
@@ -118,6 +127,9 @@
     <t xml:space="preserve">Legendary</t>
   </si>
   <si>
+    <t xml:space="preserve">Attack_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕의 끊임없는 잔소리를 들으며 억지로 휘두르다 보니 공격력이 증가합니다.</t>
   </si>
   <si>
@@ -130,6 +142,9 @@
     <t xml:space="preserve">MaxHp</t>
   </si>
   <si>
+    <t xml:space="preserve">MaxHp_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">레온의 냄비 투구와 세트 느낌이 나는 뚜껑. 최대 체력이 증가합니다.</t>
   </si>
   <si>
@@ -139,6 +154,9 @@
     <t xml:space="preserve">튼튼한 고기방패</t>
   </si>
   <si>
+    <t xml:space="preserve">MaxHp_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">맞는 건 용사가 담당하고 버티는 건 이 방패가 담당합니다. 최대 체력이 증가합니다.</t>
   </si>
   <si>
@@ -148,6 +166,9 @@
     <t xml:space="preserve">마왕의 건강검진표</t>
   </si>
   <si>
+    <t xml:space="preserve">MaxHp_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 용사의 허약함을 확인하고 작성한 건강검진표. 최대 체력이 증가합니다.</t>
   </si>
   <si>
@@ -157,6 +178,9 @@
     <t xml:space="preserve">절대 죽지 마 영양제</t>
   </si>
   <si>
+    <t xml:space="preserve">MaxHp_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">너무 쉽게 죽는 용사를 위해 마왕이 직접 만든 영양제. 최대 체력이 증가합니다.</t>
   </si>
   <si>
@@ -169,6 +193,9 @@
     <t xml:space="preserve">Defense</t>
   </si>
   <si>
+    <t xml:space="preserve">Defense_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">몬스터에게 맞을 때 덜 아프라고 마왕이 건넨 베개. 방어력이 증가합니다.</t>
   </si>
   <si>
@@ -178,6 +205,9 @@
     <t xml:space="preserve">마왕성 앞치마</t>
   </si>
   <si>
+    <t xml:space="preserve">Defense_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">요리할 때 튀는 기름을 막아주던 앞치마. 의외로 튼튼합니다.</t>
   </si>
   <si>
@@ -187,6 +217,9 @@
     <t xml:space="preserve">두꺼운 냄비 받침</t>
   </si>
   <si>
+    <t xml:space="preserve">Defense_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">냄비를 받치던 물건인데 용사가 방패로 쓰기 시작했습니다.</t>
   </si>
   <si>
@@ -196,6 +229,9 @@
     <t xml:space="preserve">맞아도 괜찮아 영양제</t>
   </si>
   <si>
+    <t xml:space="preserve">Defense_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">매번 얻어맞는 용사를 보다 못한 마왕의 특단의 조치. 방어력이 증가합니다.</t>
   </si>
   <si>
@@ -208,6 +244,9 @@
     <t xml:space="preserve">CriticalChance</t>
   </si>
   <si>
+    <t xml:space="preserve">CriChance_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">너무 눈부셔서 우연히 급소를 맞춥니다. 치명타 확률이 증가합니다.</t>
   </si>
   <si>
@@ -217,6 +256,9 @@
     <t xml:space="preserve">행운의 동전</t>
   </si>
   <si>
+    <t xml:space="preserve">CriChance_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">앞면이 나오면 운이 좋다고 믿는 낡은 동전. 치명타 확률이 증가합니다.</t>
   </si>
   <si>
@@ -226,6 +268,9 @@
     <t xml:space="preserve">급소 표시 연습장</t>
   </si>
   <si>
+    <t xml:space="preserve">CriChance_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">급소 위치를 열심히 외우게 해주는 연습장. 실제로는 잘 못 맞힙니다.</t>
   </si>
   <si>
@@ -235,6 +280,9 @@
     <t xml:space="preserve">마왕의 빨간 펜</t>
   </si>
   <si>
+    <t xml:space="preserve">CriChance_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 직접 급소에 동그라미를 쳐줍니다. 치명타 확률이 증가합니다.</t>
   </si>
   <si>
@@ -247,6 +295,9 @@
     <t xml:space="preserve">CriticalDamage</t>
   </si>
   <si>
+    <t xml:space="preserve">CriDamage_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">엉뚱하게 휘둘러도 대박 손상을 입힙니다. 치명타 피해량이 증가합니다.</t>
   </si>
   <si>
@@ -256,6 +307,9 @@
     <t xml:space="preserve">금이 간 대검</t>
   </si>
   <si>
+    <t xml:space="preserve">CriDamage_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">날은 무뎌졌지만 맞으면 여전히 아픕니다. 치명타 피해량이 증가합니다.</t>
   </si>
   <si>
@@ -265,6 +319,9 @@
     <t xml:space="preserve">마왕의 힘자랑 메달</t>
   </si>
   <si>
+    <t xml:space="preserve">CriDamage_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕성에서 힘이 세다고 자랑하는 사람에게 주는 메달입니다.</t>
   </si>
   <si>
@@ -274,6 +331,9 @@
     <t xml:space="preserve">한 방만큼은 영웅</t>
   </si>
   <si>
+    <t xml:space="preserve">CriDamage_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">평소에는 폐급이지만 한 번 제대로 맞으면 제법 아픕니다.</t>
   </si>
   <si>
@@ -286,6 +346,9 @@
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">AtkSpeed_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 급하게 만든 각성 음료. 손은 빨라지지만 정신은 그대로입니다.</t>
   </si>
   <si>
@@ -295,6 +358,9 @@
     <t xml:space="preserve">빨라지는 장갑</t>
   </si>
   <si>
+    <t xml:space="preserve">AtkSpeed_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">손을 조금 더 빠르게 움직일 수 있게 해주는 장갑입니다.</t>
   </si>
   <si>
@@ -304,6 +370,9 @@
     <t xml:space="preserve">조급한 모래시계</t>
   </si>
   <si>
+    <t xml:space="preserve">AtkSpeed_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">모래가 떨어지는 걸 보면 괜히 마음이 급해집니다. 공격 속도가 증가합니다.</t>
   </si>
   <si>
@@ -313,6 +382,9 @@
     <t xml:space="preserve">손이 먼저 움직여</t>
   </si>
   <si>
+    <t xml:space="preserve">AtkSpeed_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">생각하기 전에 손부터 움직이게 만드는 이상한 훈련법입니다.</t>
   </si>
   <si>
@@ -325,6 +397,9 @@
     <t xml:space="preserve">CooldownReduction</t>
   </si>
   <si>
+    <t xml:space="preserve">CoolDown_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕의 칼퇴근 욕구가 용사의 스킬 쿨타임까지 줄여줍니다.</t>
   </si>
   <si>
@@ -334,6 +409,9 @@
     <t xml:space="preserve">식어버린 커피</t>
   </si>
   <si>
+    <t xml:space="preserve">CoolDown_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 커피를 마시며 기다리는 시간이 아까워졌습니다.</t>
   </si>
   <si>
@@ -343,6 +421,9 @@
     <t xml:space="preserve">스킬 빨리 써! 메모</t>
   </si>
   <si>
+    <t xml:space="preserve">CoolDown_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 용사에게 붙여놓은 재촉 메모. 스킬을 빨리 사용하게 합니다.</t>
   </si>
   <si>
@@ -364,6 +445,9 @@
     <t xml:space="preserve">Accuracy</t>
   </si>
   <si>
+    <t xml:space="preserve">Accuracy_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">눈먼 칼질도 몬스터에게 정확히 맞게 해줍니다. 명중률이 증가합니다.</t>
   </si>
   <si>
@@ -373,6 +457,9 @@
     <t xml:space="preserve">표적지 한 장</t>
   </si>
   <si>
+    <t xml:space="preserve">Accuracy_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">적의 위치를 알려주는 아주 평범한 표적지입니다.</t>
   </si>
   <si>
@@ -382,6 +469,9 @@
     <t xml:space="preserve">마왕의 조준 교본</t>
   </si>
   <si>
+    <t xml:space="preserve">Accuracy_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 직접 만든 조준 교본. 읽어도 잘 맞지는 않지만 조금 나아집니다.</t>
   </si>
   <si>
@@ -391,6 +481,9 @@
     <t xml:space="preserve">손가락으로 가리키기</t>
   </si>
   <si>
+    <t xml:space="preserve">Accuracy_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 적을 손가락으로 가리켜 주면 용사도 그쪽을 봅니다.</t>
   </si>
   <si>
@@ -403,6 +496,9 @@
     <t xml:space="preserve">Evasion</t>
   </si>
   <si>
+    <t xml:space="preserve">Evasion_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">엉덩방아를 찧으며 얼떨결에 공격을 피합니다. 회피율이 증가합니다.</t>
   </si>
   <si>
@@ -412,6 +508,9 @@
     <t xml:space="preserve">구멍 난 신발</t>
   </si>
   <si>
+    <t xml:space="preserve">Evasion_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">신발에 구멍이 나 발이 자꾸 미끄러집니다. 이상하게 공격도 피합니다.</t>
   </si>
   <si>
@@ -421,6 +520,9 @@
     <t xml:space="preserve">허술한 옆걸음 교본</t>
   </si>
   <si>
+    <t xml:space="preserve">Evasion_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">제대로 피하는 법 대신 이상하게 움직이는 법을 알려줍니다.</t>
   </si>
   <si>
@@ -430,6 +532,9 @@
     <t xml:space="preserve">넘어지기 선수 인증서</t>
   </si>
   <si>
+    <t xml:space="preserve">Evasion_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">넘어지는 데에는 누구보다 진심인 용사의 인증서입니다.</t>
   </si>
   <si>
@@ -442,6 +547,9 @@
     <t xml:space="preserve">LifeSteal</t>
   </si>
   <si>
+    <t xml:space="preserve">LifeSteal_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">적의 생명력을 쪽쪽 빨아먹습니다. 용사는 왜 빨대가 있는지 모릅니다.</t>
   </si>
   <si>
@@ -451,6 +559,9 @@
     <t xml:space="preserve">흡혈 빨강사탕</t>
   </si>
   <si>
+    <t xml:space="preserve">LifeSteal_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">먹으면 힘이 난다는 수상한 사탕. 적에게서 생명력을 빼앗습니다.</t>
   </si>
   <si>
@@ -460,6 +571,9 @@
     <t xml:space="preserve">피 묻은 손수건</t>
   </si>
   <si>
+    <t xml:space="preserve">LifeSteal_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">누구의 것인지 알 수 없는 손수건. 공격할 때 생명력을 조금 회복합니다.</t>
   </si>
   <si>
@@ -469,6 +583,9 @@
     <t xml:space="preserve">한 입만</t>
   </si>
   <si>
+    <t xml:space="preserve">LifeSteal_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">적을 한 대 때리고 체력을 조금 가져옵니다. 정말 한 입만입니다.</t>
   </si>
   <si>
@@ -481,6 +598,9 @@
     <t xml:space="preserve">MoveSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">MoveSpeed_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">싸우기 싫을 때 도망치기 위한 운동화. 이동 속도가 증가합니다.</t>
   </si>
   <si>
@@ -490,6 +610,9 @@
     <t xml:space="preserve">마왕성 배달 전표</t>
   </si>
   <si>
+    <t xml:space="preserve">MoveSpeed_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕성 배달을 제시간에 끝내기 위해 만들어진 전표입니다.</t>
   </si>
   <si>
@@ -499,6 +622,9 @@
     <t xml:space="preserve">급한 용사의 신발</t>
   </si>
   <si>
+    <t xml:space="preserve">MoveSpeed_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">전투보다 도망칠 때 더 빛나는 신발입니다.</t>
   </si>
   <si>
@@ -508,6 +634,9 @@
     <t xml:space="preserve">퇴근 시간 알림</t>
   </si>
   <si>
+    <t xml:space="preserve">MoveSpeed_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">퇴근 시간이 다가오면 용사의 발걸음도 빨라집니다.</t>
   </si>
   <si>
@@ -520,6 +649,9 @@
     <t xml:space="preserve">GoldGainBonus</t>
   </si>
   <si>
+    <t xml:space="preserve">GoldBonus_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">용사의 찢어진 주머니에서 골드가 쏟아집니다. 골드 획득량이 증가합니다.</t>
   </si>
   <si>
@@ -529,6 +661,9 @@
     <t xml:space="preserve">찢어진 지갑 수선키트</t>
   </si>
   <si>
+    <t xml:space="preserve">GoldBonus_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">돈이 새는 용사의 지갑을 조금이나마 고쳐줍니다.</t>
   </si>
   <si>
@@ -538,6 +673,9 @@
     <t xml:space="preserve">황금빛 영수증</t>
   </si>
   <si>
+    <t xml:space="preserve">GoldBonus_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">어째서인지 들고 있으면 몬스터가 골드를 더 많이 떨어뜨립니다.</t>
   </si>
   <si>
@@ -547,6 +685,9 @@
     <t xml:space="preserve">마왕의 절약 장부</t>
   </si>
   <si>
+    <t xml:space="preserve">GoldBonus_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 용사의 지출을 감시하기 위해 만든 장부입니다.</t>
   </si>
   <si>
@@ -559,6 +700,9 @@
     <t xml:space="preserve">EquipmentDropRate</t>
   </si>
   <si>
+    <t xml:space="preserve">DropRate_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">몬스터들이 순순히 장비를 내놓습니다. 장비 드랍률이 증가합니다.</t>
   </si>
   <si>
@@ -566,6 +710,9 @@
   </si>
   <si>
     <t xml:space="preserve">까마귀 깃털</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DropRate_2</t>
   </si>
   <si>
     <r>
@@ -596,12 +743,18 @@
     <t xml:space="preserve">보물 탐지 나침반</t>
   </si>
   <si>
+    <t xml:space="preserve">DropRate_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">RELIC_EQUIPMENTDROPRATE_04</t>
   </si>
   <si>
     <t xml:space="preserve">마왕의 명패</t>
   </si>
   <si>
+    <t xml:space="preserve">DropRate_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕의 무장해제 명령에 따라 몬스터들이 장비를 벗습니다.</t>
   </si>
   <si>
@@ -614,6 +767,9 @@
     <t xml:space="preserve">ExpGainBonus</t>
   </si>
   <si>
+    <t xml:space="preserve">ExpBonus_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">매우 유용한 팁이 적힌 요약 노트. 경험치 획득량이 증가합니다.</t>
   </si>
   <si>
@@ -623,6 +779,9 @@
     <t xml:space="preserve">마왕의 과외 숙제</t>
   </si>
   <si>
+    <t xml:space="preserve">ExpBonus_2</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 직접 내준 숙제. 하기 싫어도 경험치는 얻습니다.</t>
   </si>
   <si>
@@ -630,6 +789,9 @@
   </si>
   <si>
     <t xml:space="preserve">컨닝 페이퍼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpBonus_3</t>
   </si>
   <si>
     <r>
@@ -660,6 +822,9 @@
     <t xml:space="preserve">마왕의 비밀 노트</t>
   </si>
   <si>
+    <t xml:space="preserve">ExpBonus_4</t>
+  </si>
+  <si>
     <t xml:space="preserve">레온의 멍청함도 극복시키는 마왕의 족집게 비밀 노트.</t>
   </si>
   <si>
@@ -672,6 +837,9 @@
     <t xml:space="preserve">RebirthPointBonus</t>
   </si>
   <si>
+    <t xml:space="preserve">RBPBonus_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">마왕이 은퇴 후 가보고 싶은 장소입니다. 환생 포인트 획득량이 증가합니다.</t>
   </si>
   <si>
@@ -679,6 +847,9 @@
   </si>
   <si>
     <t xml:space="preserve">마왕의 은퇴 계획서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBPBonus_2</t>
   </si>
   <si>
     <r>
@@ -709,6 +880,9 @@
     <t xml:space="preserve">환생 소설</t>
   </si>
   <si>
+    <t xml:space="preserve">RBPBonus_3</t>
+  </si>
+  <si>
     <t xml:space="preserve">다시 시작하면 다음 번에는 다른 삶이 나를 기다리고 있다는 내용의 소설입니다.</t>
   </si>
   <si>
@@ -716,6 +890,9 @@
   </si>
   <si>
     <t xml:space="preserve">용사의 두 번째 인생 상담권</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBPBonus_4</t>
   </si>
   <si>
     <t xml:space="preserve">환생 후에는 제발 제대로 살아보라는 마왕의 상담권입니다.</t>
@@ -757,15 +934,15 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -820,11 +997,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -961,7 +1138,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="71.38"/>
   </cols>
   <sheetData>
@@ -1050,16 +1227,19 @@
       <c r="G4" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="I4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -1071,21 +1251,24 @@
         <v>1.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="I5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -1097,21 +1280,24 @@
         <v>3.12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H6" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="I6" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
@@ -1123,24 +1309,27 @@
         <v>3.1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H7" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>12</v>
@@ -1154,19 +1343,22 @@
       <c r="G8" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="I8" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>18</v>
@@ -1175,24 +1367,27 @@
         <v>3.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H9" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I9" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>15</v>
@@ -1201,24 +1396,27 @@
         <v>3.12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H10" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>21.7</v>
@@ -1227,24 +1425,27 @@
         <v>4.65</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H11" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="I11" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>8</v>
@@ -1258,19 +1459,22 @@
       <c r="G12" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H12" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="I12" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>9</v>
@@ -1279,24 +1483,27 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H13" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="I13" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>13.75</v>
@@ -1305,24 +1512,27 @@
         <v>3.12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H14" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="I14" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>18.6</v>
@@ -1331,24 +1541,27 @@
         <v>4.65</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H15" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="I15" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>2.4</v>
@@ -1362,19 +1575,22 @@
       <c r="G16" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H16" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="I16" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>2</v>
@@ -1383,24 +1599,27 @@
         <v>0.5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H17" s="1" t="s">
+        <v>78</v>
+      </c>
       <c r="I17" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>4.38</v>
@@ -1409,24 +1628,27 @@
         <v>0.75</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H18" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="I18" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>3.88</v>
@@ -1435,24 +1657,27 @@
         <v>0.78</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H19" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="I19" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>16</v>
@@ -1466,19 +1691,22 @@
       <c r="G20" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H20" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="I20" s="1" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>18</v>
@@ -1487,24 +1715,27 @@
         <v>3.5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H21" s="1" t="s">
+        <v>95</v>
+      </c>
       <c r="I21" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>27.5</v>
@@ -1513,24 +1744,27 @@
         <v>5.62</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H22" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="I22" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>31</v>
@@ -1539,24 +1773,27 @@
         <v>6.2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H23" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="I23" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>4</v>
@@ -1570,19 +1807,22 @@
       <c r="G24" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H24" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="I24" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>4</v>
@@ -1591,24 +1831,27 @@
         <v>0.8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H25" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="I25" s="1" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>7.5</v>
@@ -1617,24 +1860,27 @@
         <v>1.5</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H26" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="I26" s="1" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>7.75</v>
@@ -1643,24 +1889,27 @@
         <v>1.55</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H27" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="I27" s="1" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>4</v>
@@ -1674,19 +1923,22 @@
       <c r="G28" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H28" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="I28" s="1" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>4</v>
@@ -1695,24 +1947,27 @@
         <v>0.8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H29" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="I29" s="1" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>7.5</v>
@@ -1721,24 +1976,27 @@
         <v>1.5</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H30" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="I30" s="1" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>7.75</v>
@@ -1747,24 +2005,27 @@
         <v>1.55</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H31" s="1" t="s">
+        <v>133</v>
+      </c>
       <c r="I31" s="1" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>4</v>
@@ -1778,19 +2039,22 @@
       <c r="G32" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H32" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="I32" s="1" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>4</v>
@@ -1799,24 +2063,27 @@
         <v>0.8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H33" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="I33" s="1" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>7.5</v>
@@ -1825,24 +2092,27 @@
         <v>1.5</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H34" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="I34" s="1" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>7.75</v>
@@ -1851,24 +2121,27 @@
         <v>1.55</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H35" s="1" t="s">
+        <v>153</v>
+      </c>
       <c r="I35" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>2.4</v>
@@ -1882,19 +2155,22 @@
       <c r="G36" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H36" s="1" t="s">
+        <v>158</v>
+      </c>
       <c r="I36" s="1" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>2.5</v>
@@ -1903,24 +2179,27 @@
         <v>0.5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H37" s="1" t="s">
+        <v>162</v>
+      </c>
       <c r="I37" s="1" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>4.38</v>
@@ -1929,24 +2208,27 @@
         <v>0.75</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H38" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="I38" s="1" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>4.65</v>
@@ -1955,24 +2237,27 @@
         <v>0.78</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H39" s="1" t="s">
+        <v>170</v>
+      </c>
       <c r="I39" s="1" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>2.4</v>
@@ -1986,19 +2271,22 @@
       <c r="G40" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H40" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="I40" s="1" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>2.5</v>
@@ -2007,24 +2295,27 @@
         <v>0.5</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H41" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="I41" s="1" t="s">
-        <v>143</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>5</v>
@@ -2033,24 +2324,27 @@
         <v>0.88</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H42" s="1" t="s">
+        <v>183</v>
+      </c>
       <c r="I42" s="1" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>139</v>
+        <v>174</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>4.65</v>
@@ -2059,24 +2353,27 @@
         <v>0.78</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H43" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="I43" s="1" t="s">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>4</v>
@@ -2090,19 +2387,22 @@
       <c r="G44" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H44" s="1" t="s">
+        <v>192</v>
+      </c>
       <c r="I44" s="1" t="s">
-        <v>153</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>4</v>
@@ -2111,24 +2411,27 @@
         <v>0.8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H45" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="I45" s="1" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>7.5</v>
@@ -2137,24 +2440,27 @@
         <v>1.5</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H46" s="1" t="s">
+        <v>200</v>
+      </c>
       <c r="I46" s="1" t="s">
-        <v>159</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>7.75</v>
@@ -2163,24 +2469,27 @@
         <v>1.55</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H47" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="I47" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>164</v>
+        <v>207</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>12</v>
@@ -2194,19 +2503,22 @@
       <c r="G48" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H48" s="1" t="s">
+        <v>209</v>
+      </c>
       <c r="I48" s="1" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>168</v>
+        <v>212</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>12</v>
@@ -2215,24 +2527,27 @@
         <v>2.5</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>28</v>
       </c>
+      <c r="H49" s="1" t="s">
+        <v>213</v>
+      </c>
       <c r="I49" s="1" t="s">
-        <v>169</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>171</v>
+        <v>216</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>22.5</v>
@@ -2241,24 +2556,27 @@
         <v>4.38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H50" s="1" t="s">
+        <v>217</v>
+      </c>
       <c r="I50" s="1" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>173</v>
+        <v>219</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>174</v>
+        <v>220</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>21.7</v>
@@ -2267,24 +2585,27 @@
         <v>4.65</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H51" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="I51" s="1" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="D52" s="1" t="n">
         <v>8</v>
@@ -2298,19 +2619,22 @@
       <c r="G52" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H52" s="1" t="s">
+        <v>226</v>
+      </c>
       <c r="I52" s="1" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>8</v>
@@ -2319,24 +2643,27 @@
         <v>1.5</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>182</v>
+      <c r="H53" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>183</v>
+        <v>232</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>184</v>
+        <v>233</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>15</v>
@@ -2345,24 +2672,27 @@
         <v>3.12</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>182</v>
+      <c r="H54" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>185</v>
+        <v>235</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>13.95</v>
@@ -2371,24 +2701,27 @@
         <v>3.1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>187</v>
+      <c r="H55" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>189</v>
+        <v>240</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>8</v>
@@ -2402,19 +2735,22 @@
       <c r="G56" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H56" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="I56" s="1" t="s">
-        <v>191</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>193</v>
+        <v>244</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>8</v>
@@ -2423,24 +2759,27 @@
         <v>1.5</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>194</v>
+      <c r="H57" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>15</v>
@@ -2449,24 +2788,27 @@
         <v>3.12</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>197</v>
+      <c r="H58" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>199</v>
+        <v>253</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="D59" s="1" t="n">
         <v>13.95</v>
@@ -2475,24 +2817,27 @@
         <v>3.1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>200</v>
+      <c r="H59" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>201</v>
+        <v>256</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>202</v>
+        <v>257</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>8</v>
@@ -2506,19 +2851,22 @@
       <c r="G60" s="1" t="n">
         <v>55</v>
       </c>
+      <c r="H60" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="I60" s="1" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>205</v>
+        <v>261</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>206</v>
+        <v>262</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D61" s="1" t="n">
         <v>12</v>
@@ -2527,24 +2875,27 @@
         <v>3</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="I61" s="3" t="s">
-        <v>207</v>
+      <c r="H61" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>208</v>
+        <v>265</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D62" s="1" t="n">
         <v>10</v>
@@ -2553,24 +2904,27 @@
         <v>2.5</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="H62" s="1" t="s">
+        <v>267</v>
+      </c>
       <c r="I62" s="1" t="s">
-        <v>210</v>
+        <v>268</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>212</v>
+        <v>270</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D63" s="1" t="n">
         <v>15.5</v>
@@ -2579,13 +2933,16 @@
         <v>3.88</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="H63" s="1" t="s">
+        <v>271</v>
+      </c>
       <c r="I63" s="1" t="s">
-        <v>213</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
